--- a/astro-site/public/dl/kit-tareas-hotel/06-fb-banquetes-eventos.xlsx
+++ b/astro-site/public/dl/kit-tareas-hotel/06-fb-banquetes-eventos.xlsx
@@ -1,16 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Banquetes y Eventos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Banquetes y Eventos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Banquetes y Eventos'!$5:$5</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -18,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -79,6 +81,11 @@
       <name val="Calibri"/>
       <color rgb="00999999"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="8">
@@ -149,54 +156,65 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="19">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="7" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -556,15 +574,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -572,6 +591,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -600,9 +620,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
         <is>
@@ -624,8 +642,25 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-hotel · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -634,18 +669,18 @@
   <sheetPr>
     <tabColor rgb="00E0F2F1"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -662,6 +697,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -839,6 +875,7 @@
       <c r="F12" s="11" t="n"/>
       <c r="G12" s="13" t="n"/>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
@@ -1035,6 +1072,7 @@
       <c r="F23" s="11" t="n"/>
       <c r="G23" s="13" t="n"/>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
@@ -1193,6 +1231,7 @@
       <c r="F32" s="11" t="n"/>
       <c r="G32" s="13" t="n"/>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
@@ -1350,6 +1389,26 @@
       <c r="E41" s="12" t="n"/>
       <c r="F41" s="11" t="n"/>
       <c r="G41" s="13" t="n"/>
+    </row>
+    <row r="42">
+      <c r="B42" s="18" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C42">
+        <f>COUNTIF(E6:E41,"✓")</f>
+        <v>3.0</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E42">
+        <f>COUNTIF(B6:B41,"?*")</f>
+        <v>30.0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="17" t="inlineStr">
@@ -1376,11 +1435,25 @@
     <mergeCell ref="A25:G25"/>
     <mergeCell ref="A43:G43"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G41">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E10 E11 E12 E16 E17 E18 E19 E20 E21 E22 E23 E27 E28 E29 E30 E31 E32 E36 E37 E38 E39 E40 E41" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E16 E17 E18 E19 E20 E21 E22 E23 E27 E28 E29 E30 E31 E32 E36 E37 E38 E39 E40 E41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-hotel/06-fb-banquetes-eventos.xlsx
+++ b/astro-site/public/dl/kit-tareas-hotel/06-fb-banquetes-eventos.xlsx
@@ -576,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -644,9 +644,38 @@
     </row>
     <row r="12"/>
     <row r="13">
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-hotel · info@aichef.pro</t>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Antes de firmar el evento:</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>▸ La primera sección se rellena AL CONFIRMAR LA RESERVA, no el día del banquete: alérgenos e intolerancias por escrito con nombre y mesa, nº de comensales garantizado, precio por comensal y qué incluye, condiciones de cancelación y aforo del salón.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>▸ El día del evento sólo se REPASAN contra el plano de sala. Cada posición con menú especial lleva camarero asignado y el plato sale identificado desde cocina.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-hotel · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -671,7 +700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -701,7 +730,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Coordinación pre-evento</t>
+          <t>Al confirmar la reserva del evento</t>
         </is>
       </c>
     </row>
@@ -748,12 +777,12 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Confirmar BEO (Banquet Event Order) con cliente/wedding planner</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>Banquetes</t>
+          <t>Recoger POR ESCRITO alérgenos, intolerancias y dietas especiales (religiosas, veganas, infantiles) con nombre y mesa de cada comensal</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>Admin</t>
         </is>
       </c>
       <c r="D6" s="11" t="n"/>
@@ -767,12 +796,12 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Verificar montaje de salón según plano aprobado (teatro, imperial, cóctel)</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>Banquetes</t>
+          <t>Cerrar con el cliente el nº de comensales garantizado y la fecha límite para modificarlo</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>Admin</t>
         </is>
       </c>
       <c r="D7" s="11" t="n"/>
@@ -786,7 +815,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Coordinar con departamentos: recepción, housekeeping, AV, seguridad</t>
+          <t>Cerrar por escrito el precio por comensal y QUÉ incluye: barra libre, recena, descorche, montaje, personal extra y horas de más</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
@@ -805,12 +834,12 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Confirmar menú definitivo, alérgenos y distribución de mesas</t>
-        </is>
-      </c>
-      <c r="C9" s="15" t="inlineStr">
-        <is>
-          <t>Cocina</t>
+          <t>Cerrar las condiciones de cancelación, la señal y el calendario de pagos, y guardarlo firmado con el BEO</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>Admin</t>
         </is>
       </c>
       <c r="D9" s="11" t="n"/>
@@ -824,12 +853,12 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Verificar equipamiento AV: proyector, micro, pantalla, traducción</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>Admin</t>
+          <t>Confirmar por escrito los menús alternativos y quién los sirve: el plato especial sale identificado desde cocina</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>Cocina</t>
         </is>
       </c>
       <c r="D10" s="11" t="n"/>
@@ -843,7 +872,7 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Coordinar timing con DJ, fotógrafo, florista u otros proveedores</t>
+          <t>Comprobar aforo del salón, salidas de emergencia y seguro de responsabilidad civil para el formato contratado</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
@@ -857,81 +886,99 @@
       <c r="G11" s="13" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Preparar habitaciones especiales con amenities si aplica (novios, VIP)</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D12" s="11" t="n"/>
-      <c r="E12" s="12" t="n"/>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="13" t="n"/>
-    </row>
-    <row r="13"/>
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Coordinación pre-evento</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Zona</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>Hora</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>Montaje de boda / cena de gala</t>
-        </is>
-      </c>
+      <c r="A14" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Confirmar BEO (Banquet Event Order) con cliente/wedding planner</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Banquetes</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="n"/>
+      <c r="E14" s="12" t="n"/>
+      <c r="F14" s="11" t="n"/>
+      <c r="G14" s="13" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>Zona</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>Responsable</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>Hora</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>Notas</t>
-        </is>
-      </c>
+      <c r="A15" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Verificar montaje de salón según plano aprobado (teatro, imperial, cóctel)</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Banquetes</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="n"/>
+      <c r="E15" s="12" t="n"/>
+      <c r="F15" s="11" t="n"/>
+      <c r="G15" s="13" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Montar mesa imperial o mesas redondas según BEO con mantelería</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>Banquetes</t>
+          <t>Coordinar con departamentos: recepción, housekeeping, AV, seguridad</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>Admin</t>
         </is>
       </c>
       <c r="D16" s="11" t="n"/>
@@ -941,16 +988,16 @@
     </row>
     <row r="17">
       <c r="A17" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Colocar cubertería completa para todos los tiempos del menú</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>Banquetes</t>
+          <t>Confirmar con cocina el menú definitivo y la distribución de mesas, y repasar los alérgenos ya recogidos al confirmar la reserva contra el plano de sala</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>Cocina</t>
         </is>
       </c>
       <c r="D17" s="11" t="n"/>
@@ -960,16 +1007,16 @@
     </row>
     <row r="18">
       <c r="A18" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Colocar centro de mesa, tarjetas de asiento y menú impreso</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>Banquetes</t>
+          <t>Verificar equipamiento AV: proyector, micro, pantalla, traducción</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>Admin</t>
         </is>
       </c>
       <c r="D18" s="11" t="n"/>
@@ -979,16 +1026,16 @@
     </row>
     <row r="19">
       <c r="A19" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Preparar cóctel de bienvenida: canapés, cava, zona de terraza/jardín</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>Banquetes</t>
+          <t>Coordinar timing con DJ, fotógrafo, florista u otros proveedores</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>Admin</t>
         </is>
       </c>
       <c r="D19" s="11" t="n"/>
@@ -998,16 +1045,16 @@
     </row>
     <row r="20">
       <c r="A20" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Servicio de mesa sincronizado: todos los platos al mismo tiempo</t>
-        </is>
-      </c>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>Banquetes</t>
+          <t>Preparar habitaciones especiales con amenities si aplica (novios, VIP)</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>Admin</t>
         </is>
       </c>
       <c r="D20" s="11" t="n"/>
@@ -1015,115 +1062,115 @@
       <c r="F20" s="11" t="n"/>
       <c r="G20" s="13" t="n"/>
     </row>
-    <row r="21">
-      <c r="A21" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>Coordinar corte de tarta/discursos con fotógrafo y DJ</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t>Banquetes</t>
-        </is>
-      </c>
-      <c r="D21" s="11" t="n"/>
-      <c r="E21" s="12" t="n"/>
-      <c r="F21" s="11" t="n"/>
-      <c r="G21" s="13" t="n"/>
-    </row>
+    <row r="21"/>
     <row r="22">
-      <c r="A22" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>Barra libre según horario pactado (controlar cierre)</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="inlineStr">
-        <is>
-          <t>Banquetes</t>
-        </is>
-      </c>
-      <c r="D22" s="11" t="n"/>
-      <c r="E22" s="12" t="n"/>
-      <c r="F22" s="11" t="n"/>
-      <c r="G22" s="13" t="n"/>
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Montaje de boda / cena de gala</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>Servicio de recena/snack nocturno si aplica</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
-        <is>
-          <t>Banquetes</t>
-        </is>
-      </c>
-      <c r="D23" s="11" t="n"/>
-      <c r="E23" s="12" t="n"/>
-      <c r="F23" s="11" t="n"/>
-      <c r="G23" s="13" t="n"/>
-    </row>
-    <row r="24"/>
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Zona</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>Hora</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Montar mesa imperial o mesas redondas según BEO con mantelería</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Banquetes</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="n"/>
+      <c r="E24" s="12" t="n"/>
+      <c r="F24" s="11" t="n"/>
+      <c r="G24" s="13" t="n"/>
+    </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>Convención / Congreso</t>
-        </is>
-      </c>
+      <c r="A25" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>Colocar cubertería completa para todos los tiempos del menú</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>Banquetes</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="n"/>
+      <c r="E25" s="12" t="n"/>
+      <c r="F25" s="11" t="n"/>
+      <c r="G25" s="13" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>Zona</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Responsable</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>Hora</t>
-        </is>
-      </c>
-      <c r="G26" s="7" t="inlineStr">
-        <is>
-          <t>Notas</t>
-        </is>
-      </c>
+      <c r="A26" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>Colocar centro de mesa, tarjetas de asiento y menú impreso</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>Banquetes</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="n"/>
+      <c r="E26" s="12" t="n"/>
+      <c r="F26" s="11" t="n"/>
+      <c r="G26" s="13" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Verificar montaje de sala plenaria según formato BEO</t>
+          <t>Marcar en el plano de sala las posiciones con menú especial o alérgeno y asignar quién sirve cada una: el plato alternativo sale marcado desde cocina y no se cruza con el resto del pase</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
@@ -1138,11 +1185,11 @@
     </row>
     <row r="28">
       <c r="A28" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Montar coffee break mañana: café, zumos, bollería, fruta, mini-sándwiches</t>
+          <t>Preparar cóctel de bienvenida: canapés, cava, zona de terraza/jardín</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
@@ -1157,11 +1204,11 @@
     </row>
     <row r="29">
       <c r="A29" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Servir almuerzo según formato: buffet, box lunch o sentado</t>
+          <t>Servicio de mesa sincronizado: todos los platos al mismo tiempo</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
@@ -1176,11 +1223,11 @@
     </row>
     <row r="30">
       <c r="A30" s="8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Coffee break tarde (variar vs. mañana): snacks, smoothies, fruta</t>
+          <t>Coordinar corte de tarta/discursos con fotógrafo y DJ</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
@@ -1195,11 +1242,11 @@
     </row>
     <row r="31">
       <c r="A31" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Mantener estación de agua y café disponible todo el día</t>
+          <t>Barra libre según horario pactado (controlar cierre)</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
@@ -1214,11 +1261,11 @@
     </row>
     <row r="32">
       <c r="A32" s="8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>Cocktail networking final: canapés, barra de cócteles</t>
+          <t>Servicio de recena/snack nocturno si aplica</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
@@ -1235,7 +1282,7 @@
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Desmontaje y cierre</t>
+          <t>Convención / Congreso</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1329,7 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>Desmontar salón según protocolo: mesas, sillas, decoración, AV</t>
+          <t>Verificar montaje de sala plenaria según formato BEO</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
@@ -1301,7 +1348,7 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>Inventariar cubertería, cristalería y menaje (reportar roturas)</t>
+          <t>Montar coffee break mañana: café, zumos, bollería, fruta, mini-sándwiches</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
@@ -1320,12 +1367,12 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Limpiar salón a fondo: suelo, moqueta, paredes, baños</t>
-        </is>
-      </c>
-      <c r="C38" s="16" t="inlineStr">
-        <is>
-          <t>Limpieza</t>
+          <t>Servir almuerzo según formato: buffet, box lunch o sentado</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>Banquetes</t>
         </is>
       </c>
       <c r="D38" s="11" t="n"/>
@@ -1339,12 +1386,12 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>Cerrar caja de banquetes y conciliar con factura del evento</t>
-        </is>
-      </c>
-      <c r="C39" s="14" t="inlineStr">
-        <is>
-          <t>Admin</t>
+          <t>Coffee break tarde (variar vs. mañana): snacks, smoothies, fruta</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>Banquetes</t>
         </is>
       </c>
       <c r="D39" s="11" t="n"/>
@@ -1358,12 +1405,12 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>Registrar feedback del cliente y enviar encuesta de satisfacción</t>
-        </is>
-      </c>
-      <c r="C40" s="14" t="inlineStr">
-        <is>
-          <t>Admin</t>
+          <t>Mantener estación de agua y café disponible todo el día</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>Banquetes</t>
         </is>
       </c>
       <c r="D40" s="11" t="n"/>
@@ -1377,12 +1424,12 @@
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>Late check-out coordinado con recepción si procede</t>
-        </is>
-      </c>
-      <c r="C41" s="14" t="inlineStr">
-        <is>
-          <t>Admin</t>
+          <t>Cocktail networking final: canapés, barra de cócteles</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>Banquetes</t>
         </is>
       </c>
       <c r="D41" s="11" t="n"/>
@@ -1390,59 +1437,219 @@
       <c r="F41" s="11" t="n"/>
       <c r="G41" s="13" t="n"/>
     </row>
-    <row r="42">
-      <c r="B42" s="18" t="inlineStr">
+    <row r="42"/>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Desmontaje y cierre</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>Zona</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>Hora</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>Desmontar salón según protocolo: mesas, sillas, decoración, AV</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>Banquetes</t>
+        </is>
+      </c>
+      <c r="D45" s="11" t="n"/>
+      <c r="E45" s="12" t="n"/>
+      <c r="F45" s="11" t="n"/>
+      <c r="G45" s="13" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>Inventariar cubertería, cristalería y menaje (reportar roturas)</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>Banquetes</t>
+        </is>
+      </c>
+      <c r="D46" s="11" t="n"/>
+      <c r="E46" s="12" t="n"/>
+      <c r="F46" s="11" t="n"/>
+      <c r="G46" s="13" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>Limpiar salón a fondo: suelo, moqueta, paredes, baños</t>
+        </is>
+      </c>
+      <c r="C47" s="16" t="inlineStr">
+        <is>
+          <t>Limpieza</t>
+        </is>
+      </c>
+      <c r="D47" s="11" t="n"/>
+      <c r="E47" s="12" t="n"/>
+      <c r="F47" s="11" t="n"/>
+      <c r="G47" s="13" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>Cerrar caja de banquetes y conciliar con factura del evento</t>
+        </is>
+      </c>
+      <c r="C48" s="14" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D48" s="11" t="n"/>
+      <c r="E48" s="12" t="n"/>
+      <c r="F48" s="11" t="n"/>
+      <c r="G48" s="13" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>Registrar feedback del cliente y enviar encuesta de satisfacción</t>
+        </is>
+      </c>
+      <c r="C49" s="14" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D49" s="11" t="n"/>
+      <c r="E49" s="12" t="n"/>
+      <c r="F49" s="11" t="n"/>
+      <c r="G49" s="13" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>Late check-out coordinado con recepción si procede</t>
+        </is>
+      </c>
+      <c r="C50" s="14" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="n"/>
+      <c r="E50" s="12" t="n"/>
+      <c r="F50" s="11" t="n"/>
+      <c r="G50" s="13" t="n"/>
+    </row>
+    <row r="51">
+      <c r="B51" s="18" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C42">
-        <f>COUNTIF(E6:E41,"✓")</f>
-        <v>3.0</v>
-      </c>
-      <c r="D42" t="inlineStr">
+      <c r="C51">
+        <f>COUNTIFS(B6:B50,"?*",E6:E50,"✓")-COUNTIFS(B6:B50,"Tarea",E6:E50,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D51" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="E42">
-        <f>COUNTIF(B6:B41,"?*")</f>
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="17" t="inlineStr">
+      <c r="E51">
+        <f>COUNTIF(B6:B50,"?*")-COUNTIF(B6:B50,"Tarea")-COUNTIF(E6:E50,"N/A")</f>
+        <v>34.0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="17" t="inlineStr">
         <is>
           <t>Firma responsable: _________________  Fecha: ___/___/______</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="17" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="17" t="inlineStr">
         <is>
           <t>© 2026 AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
+    <mergeCell ref="A52:G52"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A53:G53"/>
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A44:G44"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A43:G43"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A14:G14"/>
     <mergeCell ref="A34:G34"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="A43:G43"/>
+    <mergeCell ref="A22:G22"/>
   </mergeCells>
-  <conditionalFormatting sqref="A6:G41">
+  <conditionalFormatting sqref="A6:G50">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$E6="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E16 E17 E18 E19 E20 E21 E22 E23 E27 E28 E29 E30 E31 E32 E36 E37 E38 E39 E40 E41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E14 E15 E16 E17 E18 E19 E20 E24 E25 E26 E27 E28 E29 E30 E31 E32 E36 E37 E38 E39 E40 E41 E45 E46 E47 E48 E49 E50" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>

--- a/astro-site/public/dl/kit-tareas-hotel/06-fb-banquetes-eventos.xlsx
+++ b/astro-site/public/dl/kit-tareas-hotel/06-fb-banquetes-eventos.xlsx
@@ -1634,12 +1634,12 @@
   <mergeCells count="9">
     <mergeCell ref="A52:G52"/>
     <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A4:G4"/>
     <mergeCell ref="A53:G53"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A43:G43"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A43:G43"/>
     <mergeCell ref="A22:G22"/>
   </mergeCells>
   <conditionalFormatting sqref="A6:G50">
